--- a/sessions_summary.xlsx
+++ b/sessions_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Storage\MATLAB\ThalamocorticalLoop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pri\Storage\Projects\ThalamoCorticalNetwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C42A3A-14D8-4719-97C2-E0E4F1E4A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343FDA28-D17A-43BC-9468-F9259B1BBC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="6" r:id="rId1"/>
@@ -20,17 +20,28 @@
     <sheet name="Lemmy-Kaining" sheetId="3" r:id="rId5"/>
     <sheet name="Slayer-Kaining" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="191">
   <si>
     <t>P3</t>
   </si>
@@ -486,6 +497,215 @@
   </si>
   <si>
     <t>~400</t>
+  </si>
+  <si>
+    <t>Pre valid duration</t>
+  </si>
+  <si>
+    <t>overall valid duration</t>
+  </si>
+  <si>
+    <t>01232026-008</t>
+  </si>
+  <si>
+    <t>01302026-008</t>
+  </si>
+  <si>
+    <t>02052026-008</t>
+  </si>
+  <si>
+    <t>02122026-008</t>
+  </si>
+  <si>
+    <t>01232026-001</t>
+  </si>
+  <si>
+    <t>01302026-001</t>
+  </si>
+  <si>
+    <t>02052026-001</t>
+  </si>
+  <si>
+    <t>02122026-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest </t>
+  </si>
+  <si>
+    <t>Longest pre only</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Total valid duration </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Longest continuous phase </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Total valid duration </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pre&amp;Post</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Longest continuous phase </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pre&amp;Post</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (s)</t>
+    </r>
+  </si>
+  <si>
+    <t>Training failed</t>
   </si>
 </sst>
 </file>
@@ -528,7 +748,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -571,8 +791,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -1067,11 +1299,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1196,7 +1474,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
@@ -1288,30 +1565,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1345,9 +1598,130 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,9 +1745,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1411,7 +1785,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1517,7 +1891,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1659,7 +2033,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1668,189 +2042,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E51CD7-F882-46FB-A302-DE4F0A9E1B83}">
   <dimension ref="B3:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="4" max="6" width="12.81640625" style="105" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="6" width="12.85546875" style="104" customWidth="1"/>
     <col min="7" max="11" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="129" t="s">
+    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="D4" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="131" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="128"/>
-    </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="130"/>
-      <c r="D5" s="106" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
+    </row>
+    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="117"/>
+      <c r="D5" s="105" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="107" t="s">
+      <c r="E5" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="108" t="s">
+      <c r="F5" s="107" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="109" t="s">
+      <c r="G5" s="108" t="s">
         <v>104</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="73" t="s">
+      <c r="I5" s="72" t="s">
         <v>106</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K5" s="78" t="s">
+      <c r="K5" s="77" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C6" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="91">
         <v>5</v>
       </c>
-      <c r="E6" s="103">
+      <c r="E6" s="102">
         <v>8</v>
       </c>
-      <c r="F6" s="94">
+      <c r="F6" s="93">
         <v>5</v>
       </c>
-      <c r="G6" s="95">
+      <c r="G6" s="94">
         <v>18</v>
       </c>
       <c r="H6" s="58"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="75"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="74"/>
       <c r="K6" s="57"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C7" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="96">
+      <c r="E7" s="95">
         <v>1</v>
       </c>
-      <c r="F7" s="97">
+      <c r="F7" s="96">
         <v>1</v>
       </c>
-      <c r="G7" s="98">
+      <c r="G7" s="97">
         <v>10</v>
       </c>
       <c r="H7" s="53"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="76"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="75"/>
       <c r="K7" s="54"/>
     </row>
-    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C8" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="99">
+      <c r="D8" s="98">
         <v>0</v>
       </c>
-      <c r="E8" s="100">
+      <c r="E8" s="99">
         <v>5</v>
       </c>
-      <c r="F8" s="101" t="s">
+      <c r="F8" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="102">
+      <c r="G8" s="101">
         <v>8</v>
       </c>
       <c r="H8" s="56"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="77"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="76"/>
       <c r="K8" s="55"/>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C9" s="72"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="72"/>
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="71"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="71"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="73"/>
+      <c r="I9" s="72"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="72"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="125" t="s">
+      <c r="K9" s="71"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="112" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="93"/>
       <c r="G10" s="57" t="s">
         <v>150</v>
       </c>
       <c r="H10" s="58"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="75"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="74"/>
       <c r="K10" s="57"/>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="125"/>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="112"/>
       <c r="C11" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="99"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="101"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="100"/>
       <c r="G11" s="55" t="s">
         <v>151</v>
       </c>
       <c r="H11" s="56"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="77"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="76"/>
       <c r="K11" s="55"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D14" s="125" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D14" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125" t="s">
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125" t="s">
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="125" t="s">
+      <c r="K14" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="125" t="s">
+      <c r="L14" s="112" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D15" s="44" t="s">
         <v>124</v>
       </c>
@@ -1869,9 +2243,9 @@
       <c r="I15" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1891,23 +2265,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FFE666-9548-4978-AD59-82159C4DB165}">
-  <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultColWidth="5.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="5.453125" style="1"/>
-    <col min="7" max="7" width="6.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.453125" style="1"/>
-    <col min="12" max="12" width="4.1796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.26953125" customWidth="1"/>
-    <col min="14" max="14" width="55.26953125" customWidth="1"/>
-    <col min="15" max="15" width="31" customWidth="1"/>
+    <col min="5" max="6" width="5.42578125" style="1"/>
+    <col min="7" max="7" width="6.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.42578125" style="1"/>
+    <col min="12" max="12" width="4.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" customWidth="1"/>
+    <col min="16" max="16" width="55.28515625" customWidth="1"/>
+    <col min="17" max="17" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
         <v>114</v>
       </c>
@@ -1920,23 +2296,30 @@
       <c r="D1" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="132" t="s">
+      <c r="E1" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="132"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="134" t="s">
+      <c r="F1" s="119"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="132"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="134" t="s">
+      <c r="I1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="132"/>
-      <c r="M1" s="133"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="L1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" s="123" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1" s="123"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
         <v>26</v>
       </c>
@@ -1974,11 +2357,13 @@
       <c r="M2" s="20">
         <v>49</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="s">
         <v>27</v>
       </c>
@@ -2016,11 +2401,13 @@
       <c r="M3" s="11">
         <v>21</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="s">
         <v>28</v>
       </c>
@@ -2058,11 +2445,13 @@
       <c r="M4" s="4">
         <v>6</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>29</v>
       </c>
@@ -2100,15 +2489,17 @@
       <c r="M5" s="11">
         <v>19</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="79" t="s">
+    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="31"/>
@@ -2142,11 +2533,13 @@
       <c r="M6" s="36">
         <v>6</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="126"/>
+      <c r="O6" s="126"/>
+      <c r="P6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
         <v>62</v>
       </c>
@@ -2186,102 +2579,108 @@
       <c r="M7" s="11">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="80" t="s">
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="82" t="s">
+      <c r="E8" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="F8" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="82">
         <v>43</v>
       </c>
-      <c r="H8" s="84" t="s">
+      <c r="H8" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="85" t="s">
+      <c r="I8" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="80">
         <v>16</v>
       </c>
-      <c r="K8" s="86" t="s">
+      <c r="K8" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="82" t="s">
+      <c r="L8" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="80">
         <v>5</v>
       </c>
-      <c r="N8" s="85" t="s">
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="80" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="87" t="s">
+      <c r="F9" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="88">
+      <c r="G9" s="87">
         <v>64</v>
       </c>
-      <c r="H9" s="84" t="s">
+      <c r="H9" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="85" t="s">
+      <c r="I9" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="81">
+      <c r="J9" s="80">
         <v>0</v>
       </c>
-      <c r="K9" s="86" t="s">
+      <c r="K9" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="82" t="s">
+      <c r="L9" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="81">
+      <c r="M9" s="80">
         <v>31</v>
       </c>
-      <c r="N9" s="85" t="s">
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>65</v>
       </c>
@@ -2321,8 +2720,10 @@
       <c r="M10" s="20">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N10" s="124"/>
+      <c r="O10" s="124"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
         <v>66</v>
       </c>
@@ -2362,8 +2763,10 @@
       <c r="M11" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N11" s="128"/>
+      <c r="O11" s="128"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
         <v>67</v>
       </c>
@@ -2403,8 +2806,10 @@
       <c r="M12" s="20">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N12" s="124"/>
+      <c r="O12" s="124"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
         <v>68</v>
       </c>
@@ -2444,11 +2849,13 @@
       <c r="M13" s="3">
         <v>53</v>
       </c>
-      <c r="O13" t="s">
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="Q13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
         <v>69</v>
       </c>
@@ -2488,14 +2895,16 @@
       <c r="M14" s="3">
         <v>54</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
         <v>70</v>
       </c>
@@ -2535,11 +2944,13 @@
       <c r="M15" s="3">
         <v>49</v>
       </c>
-      <c r="O15" t="s">
+      <c r="N15" s="129"/>
+      <c r="O15" s="129"/>
+      <c r="Q15" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
         <v>71</v>
       </c>
@@ -2579,11 +2990,13 @@
       <c r="M16" s="20">
         <v>40</v>
       </c>
-      <c r="O16" t="s">
+      <c r="N16" s="124"/>
+      <c r="O16" s="124"/>
+      <c r="Q16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>72</v>
       </c>
@@ -2623,11 +3036,13 @@
       <c r="M17" s="45">
         <v>39</v>
       </c>
-      <c r="O17" t="s">
+      <c r="N17" s="129"/>
+      <c r="O17" s="129"/>
+      <c r="Q17" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
         <v>73</v>
       </c>
@@ -2667,11 +3082,13 @@
       <c r="M18" s="3">
         <v>32</v>
       </c>
-      <c r="O18" t="s">
+      <c r="N18" s="129"/>
+      <c r="O18" s="129"/>
+      <c r="Q18" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
         <v>74</v>
       </c>
@@ -2711,11 +3128,13 @@
       <c r="M19" s="3">
         <v>23</v>
       </c>
-      <c r="O19" t="s">
+      <c r="N19" s="129"/>
+      <c r="O19" s="129"/>
+      <c r="Q19" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
         <v>75</v>
       </c>
@@ -2755,11 +3174,13 @@
       <c r="M20" s="3">
         <v>26</v>
       </c>
-      <c r="O20" t="s">
+      <c r="N20" s="129"/>
+      <c r="O20" s="129"/>
+      <c r="Q20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
         <v>76</v>
       </c>
@@ -2799,11 +3220,13 @@
       <c r="M21" s="3">
         <v>36</v>
       </c>
-      <c r="O21" t="s">
+      <c r="N21" s="129"/>
+      <c r="O21" s="129"/>
+      <c r="Q21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="44"/>
       <c r="C22" s="44"/>
@@ -2813,8 +3236,10 @@
       <c r="J22" s="3"/>
       <c r="K22" s="6"/>
       <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N22" s="129"/>
+      <c r="O22" s="129"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
         <v>33</v>
       </c>
@@ -2835,8 +3260,10 @@
         <f>SUM(M7:M16)</f>
         <v>302</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N23" s="129"/>
+      <c r="O23" s="129"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -2855,8 +3282,10 @@
         <f>SUM(M2:M16)</f>
         <v>403</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N24" s="129"/>
+      <c r="O24" s="129"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D25" s="3"/>
       <c r="H25" s="2" t="s">
         <v>8</v>
@@ -2867,8 +3296,10 @@
       <c r="J25" s="3"/>
       <c r="K25" s="6"/>
       <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N25" s="129"/>
+      <c r="O25" s="129"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D26" s="3"/>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -2879,8 +3310,10 @@
       <c r="J26" s="3"/>
       <c r="K26" s="6"/>
       <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N26" s="129"/>
+      <c r="O26" s="129"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D27" s="3"/>
       <c r="H27" s="2" t="s">
         <v>8</v>
@@ -2891,39 +3324,47 @@
       <c r="J27" s="3"/>
       <c r="K27" s="6"/>
       <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N27" s="129"/>
+      <c r="O27" s="129"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D28" s="3"/>
       <c r="H28" s="2"/>
       <c r="J28" s="3"/>
       <c r="K28" s="6"/>
       <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N28" s="129"/>
+      <c r="O28" s="129"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>
       <c r="H29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="6"/>
       <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N29" s="129"/>
+      <c r="O29" s="129"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D30" s="3"/>
       <c r="H30" s="2"/>
       <c r="J30" s="3"/>
       <c r="K30" s="6"/>
       <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N30" s="129"/>
+      <c r="O30" s="129"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D31" s="3"/>
       <c r="H31" s="2"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D32" s="3"/>
       <c r="H32" s="2"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D33" s="3"/>
       <c r="H33" s="2"/>
       <c r="J33" s="3"/>
@@ -2943,15 +3384,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC68E12D-C9CD-4DEC-A7DD-D60B42882618}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="29.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" style="50" customWidth="1"/>
-    <col min="2" max="4" width="17.26953125" style="50" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" style="50" customWidth="1"/>
-    <col min="6" max="16384" width="29.81640625" style="50"/>
+    <col min="1" max="1" width="19.85546875" style="50" customWidth="1"/>
+    <col min="2" max="4" width="17.28515625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" style="50" customWidth="1"/>
+    <col min="6" max="16384" width="29.85546875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="59" t="s">
         <v>114</v>
       </c>
@@ -2961,14 +3402,14 @@
       <c r="C1" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="68" t="s">
         <v>79</v>
       </c>
       <c r="E1" s="61"/>
       <c r="F1" s="61"/>
       <c r="G1" s="62"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="63"/>
       <c r="B2" s="50" t="s">
         <v>42</v>
@@ -2984,7 +3425,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="63"/>
       <c r="B3" s="50" t="s">
         <v>43</v>
@@ -3000,7 +3441,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="63"/>
       <c r="B4" s="50" t="s">
         <v>44</v>
@@ -3016,7 +3457,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="63"/>
       <c r="B5" s="50" t="s">
         <v>45</v>
@@ -3032,7 +3473,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="63"/>
       <c r="B6" s="50" t="s">
         <v>46</v>
@@ -3048,7 +3489,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="63"/>
       <c r="B7" s="50" t="s">
         <v>47</v>
@@ -3064,28 +3505,28 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="89"/>
-      <c r="B8" s="90" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="88"/>
+      <c r="B8" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="91" t="s">
+      <c r="D8" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="90" t="s">
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="I8" s="90" t="s">
+      <c r="I8" s="89" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
       <c r="B9" s="50" t="s">
         <v>49</v>
@@ -3101,7 +3542,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="63"/>
       <c r="B10" s="50" t="s">
         <v>50</v>
@@ -3117,28 +3558,28 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="122" t="s">
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="123" t="s">
+      <c r="C11" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="124" t="s">
+      <c r="D11" s="111" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90" t="s">
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="89" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>78</v>
       </c>
@@ -3163,335 +3604,573 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD31B0A-8ACD-468E-8C67-02F9624BD3CF}">
-  <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr defaultColWidth="29.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" style="50" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" style="50" customWidth="1"/>
-    <col min="4" max="4" width="23.1796875" style="50" customWidth="1"/>
-    <col min="5" max="13" width="6.453125" style="50" customWidth="1"/>
-    <col min="14" max="14" width="24.54296875" style="50" customWidth="1"/>
-    <col min="15" max="15" width="16.453125" style="50" customWidth="1"/>
-    <col min="16" max="16384" width="29.81640625" style="50"/>
+    <col min="1" max="1" width="18.85546875" style="50" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="50" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="50" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="50" customWidth="1"/>
+    <col min="5" max="13" width="6.42578125" style="50" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" style="50" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" style="50" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" style="50" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" style="50" customWidth="1"/>
+    <col min="18" max="16384" width="29.85546875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:19" s="131" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="135" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="135" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="135" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="135" t="s">
+      <c r="E1" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135" t="s">
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135" t="s">
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="50" t="s">
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
+      <c r="N1" s="132" t="s">
+        <v>147</v>
+      </c>
+      <c r="O1" s="132" t="s">
+        <v>163</v>
+      </c>
+      <c r="P1" s="132" t="s">
         <v>146</v>
       </c>
-      <c r="O1" s="50" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="63" t="s">
+      <c r="Q1" s="132" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="131" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="174" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="175" t="s">
+        <v>186</v>
+      </c>
+      <c r="O2" s="173" t="s">
+        <v>187</v>
+      </c>
+      <c r="P2" s="172" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q2" s="173" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B3" s="138" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C3" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D3" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="E3" s="156" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="F3" s="156" t="s">
         <v>141</v>
       </c>
-      <c r="G2" s="111">
+      <c r="G3" s="139">
         <v>8</v>
       </c>
-      <c r="H2" s="112" t="s">
+      <c r="H3" s="140" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="113" t="s">
+      <c r="I3" s="157" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="114">
+      <c r="J3" s="141">
         <v>3</v>
       </c>
-      <c r="K2" s="115" t="s">
+      <c r="K3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="110" t="s">
+      <c r="L3" s="156" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="114">
+      <c r="M3" s="157">
         <v>0</v>
       </c>
-      <c r="N2">
+      <c r="N3" s="176">
         <v>231</v>
       </c>
-      <c r="O2">
+      <c r="O3" s="159">
+        <v>33</v>
+      </c>
+      <c r="P3" s="158">
         <v>231</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="63" t="s">
+      <c r="Q3" s="159">
+        <v>33</v>
+      </c>
+      <c r="R3" s="122">
+        <f>J3*M3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B4" s="136" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C4" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D4" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="E4" s="156" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="110" t="s">
+      <c r="F4" s="156" t="s">
         <v>141</v>
       </c>
-      <c r="G3" s="111">
+      <c r="G4" s="139">
         <v>12</v>
       </c>
-      <c r="H3" s="112" t="s">
+      <c r="H4" s="140" t="s">
         <v>142</v>
       </c>
-      <c r="I3" s="113" t="s">
+      <c r="I4" s="157" t="s">
         <v>143</v>
       </c>
-      <c r="J3" s="114">
+      <c r="J4" s="141">
         <v>10</v>
       </c>
-      <c r="K3" s="115" t="s">
+      <c r="K4" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="110" t="s">
+      <c r="L4" s="156" t="s">
         <v>144</v>
       </c>
-      <c r="M3" s="114">
+      <c r="M4" s="157">
         <v>23</v>
       </c>
-      <c r="N3">
+      <c r="N4" s="176">
+        <v>232</v>
+      </c>
+      <c r="O4" s="159">
+        <v>33</v>
+      </c>
+      <c r="P4" s="158">
         <v>112</v>
       </c>
-      <c r="O3">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="63" t="s">
+      <c r="Q4" s="159">
+        <v>24</v>
+      </c>
+      <c r="R4" s="122">
+        <f>J4*M4</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B5" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C5" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D5" s="143" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="110" t="s">
+      <c r="E5" s="156" t="s">
         <v>139</v>
       </c>
-      <c r="F4" s="110" t="s">
+      <c r="F5" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="111">
+      <c r="G5" s="139">
         <v>20</v>
       </c>
-      <c r="H4" s="112" t="s">
+      <c r="H5" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="113" t="s">
+      <c r="I5" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="114">
+      <c r="J5" s="141">
         <v>9</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="K5" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="L4" s="110" t="s">
+      <c r="L5" s="156" t="s">
         <v>145</v>
       </c>
-      <c r="M4" s="114">
+      <c r="M5" s="157">
         <v>25</v>
       </c>
-      <c r="N4">
+      <c r="N5" s="176">
+        <v>230</v>
+      </c>
+      <c r="O5" s="159">
+        <v>60</v>
+      </c>
+      <c r="P5" s="158">
         <v>100</v>
       </c>
-      <c r="O4">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="Q5" s="159">
+        <v>38</v>
+      </c>
+      <c r="R5" s="122">
+        <f>J5*M5</f>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B6" s="136" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C6" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D6" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E6" s="160" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="110" t="s">
+      <c r="F6" s="160" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="111">
+      <c r="G6" s="145">
         <v>9</v>
       </c>
-      <c r="H5" s="112" t="s">
+      <c r="H6" s="146" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="113" t="s">
+      <c r="I6" s="161" t="s">
         <v>143</v>
       </c>
-      <c r="J5" s="114">
+      <c r="J6" s="147">
         <v>11</v>
       </c>
-      <c r="K5" s="115" t="s">
+      <c r="K6" s="148" t="s">
         <v>142</v>
       </c>
-      <c r="L5" s="110" t="s">
+      <c r="L6" s="160" t="s">
         <v>145</v>
       </c>
-      <c r="M5" s="114">
+      <c r="M6" s="161">
         <v>38</v>
       </c>
-      <c r="N5">
+      <c r="N6" s="177">
+        <v>90</v>
+      </c>
+      <c r="O6" s="163">
+        <v>17</v>
+      </c>
+      <c r="P6" s="162">
         <v>80</v>
       </c>
-      <c r="O5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="63" t="s">
+      <c r="Q6" s="163">
+        <v>17</v>
+      </c>
+      <c r="R6" s="122">
+        <f>J6*M6</f>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B7" s="136" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C7" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D7" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="116" t="s">
+      <c r="E7" s="149" t="s">
         <v>139</v>
       </c>
-      <c r="F6" s="116" t="s">
+      <c r="F7" s="149" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="117">
+      <c r="G7" s="150">
         <v>18</v>
       </c>
-      <c r="H6" s="118" t="s">
+      <c r="H7" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="I6" s="119" t="s">
+      <c r="I7" s="152" t="s">
         <v>143</v>
       </c>
-      <c r="J6" s="120">
+      <c r="J7" s="153">
         <v>17</v>
       </c>
-      <c r="K6" s="121" t="s">
+      <c r="K7" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="116" t="s">
+      <c r="L7" s="149" t="s">
         <v>145</v>
       </c>
-      <c r="M6" s="120">
+      <c r="M7" s="152">
         <v>19</v>
       </c>
-      <c r="N6">
+      <c r="N7" s="177">
+        <v>187</v>
+      </c>
+      <c r="O7" s="163">
+        <v>50</v>
+      </c>
+      <c r="P7" s="162">
         <v>35</v>
       </c>
-      <c r="O6">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="63"/>
-      <c r="D7" s="64" t="s">
+      <c r="Q7" s="163" t="s">
+        <v>165</v>
+      </c>
+      <c r="R7" s="122">
+        <f>J7*M7</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="136" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="64"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="63"/>
-      <c r="D8" s="64" t="s">
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="144" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="164"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="164" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8" s="164"/>
+      <c r="L8" s="164"/>
+      <c r="M8" s="164" t="s">
+        <v>171</v>
+      </c>
+      <c r="N8" s="177" t="s">
+        <v>166</v>
+      </c>
+      <c r="O8" s="163" t="s">
+        <v>167</v>
+      </c>
+      <c r="P8" s="162" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q8" s="163" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="136" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="144" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="64"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="63"/>
-      <c r="D9" s="64" t="s">
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="G9" s="144" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="164"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="164"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164" t="s">
+        <v>164</v>
+      </c>
+      <c r="N9" s="177" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9" s="163" t="s">
+        <v>170</v>
+      </c>
+      <c r="P9" s="162" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q9" s="163" t="s">
+        <v>172</v>
+      </c>
+      <c r="S9" s="179" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="136" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="64"/>
-    </row>
-    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="63"/>
-      <c r="D10" s="64"/>
-      <c r="G10" s="64"/>
-    </row>
-    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="68"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="62"/>
-      <c r="N11" s="50" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="67"/>
+      <c r="E10" s="164"/>
+      <c r="F10" s="164"/>
+      <c r="G10" s="144" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="164"/>
+      <c r="I10" s="164"/>
+      <c r="J10" s="164" t="s">
+        <v>182</v>
+      </c>
+      <c r="K10" s="164"/>
+      <c r="L10" s="164"/>
+      <c r="M10" s="164" t="s">
+        <v>183</v>
+      </c>
+      <c r="N10" s="177" t="s">
+        <v>173</v>
+      </c>
+      <c r="O10" s="163" t="s">
+        <v>174</v>
+      </c>
+      <c r="P10" s="162" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q10" s="163" t="s">
+        <v>176</v>
+      </c>
+      <c r="S10" s="179" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="136" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="165" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="165" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="166"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="166" t="s">
+        <v>184</v>
+      </c>
+      <c r="K11" s="166"/>
+      <c r="L11" s="166"/>
+      <c r="M11" s="166" t="s">
+        <v>185</v>
+      </c>
+      <c r="N11" s="178">
+        <v>409</v>
+      </c>
+      <c r="O11" s="168">
+        <v>49</v>
+      </c>
+      <c r="P11" s="167">
+        <v>305</v>
+      </c>
+      <c r="Q11" s="168">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="63"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="64"/>
       <c r="E12" s="66"/>
       <c r="F12" s="66"/>
       <c r="G12" s="67"/>
+      <c r="N12" s="130"/>
+      <c r="O12" s="130"/>
+      <c r="P12" s="130" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q12" s="130"/>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="67"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3507,7 +4186,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624E48F4-7931-4929-AE47-4DEF71FFC465}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3516,7 +4195,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD8B24D-05CA-4D65-9A42-9A76302C7CF2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sessions_summary.xlsx
+++ b/sessions_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Storage\MATLAB\ThalamocorticalLoop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C42A3A-14D8-4719-97C2-E0E4F1E4A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D001818-A0D5-41DE-8CAB-1F04FFECAF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="6" r:id="rId1"/>
@@ -143,12 +143,6 @@
     <t>02022024-001</t>
   </si>
   <si>
-    <t>20, 18</t>
-  </si>
-  <si>
-    <t>35, 18</t>
-  </si>
-  <si>
     <t>02092024-001</t>
   </si>
   <si>
@@ -486,6 +480,12 @@
   </si>
   <si>
     <t>~400</t>
+  </si>
+  <si>
+    <t>Thal 20-18</t>
+  </si>
+  <si>
+    <t>Thal 35-18</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1071,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1347,6 +1347,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1679,16 +1682,16 @@
     <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C4" s="129" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" s="127"/>
       <c r="F4" s="127"/>
       <c r="G4" s="128"/>
       <c r="H4" s="131" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I4" s="127"/>
       <c r="J4" s="127"/>
@@ -1697,33 +1700,33 @@
     <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="130"/>
       <c r="D5" s="106" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="107" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="108" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="108" t="s">
-        <v>131</v>
-      </c>
       <c r="G5" s="109" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="73" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="K5" s="78" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C6" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D6" s="92">
         <v>5</v>
@@ -1744,10 +1747,10 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C7" s="54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D7" s="104" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" s="96">
         <v>1</v>
@@ -1765,7 +1768,7 @@
     </row>
     <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C8" s="55" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" s="99">
         <v>0</v>
@@ -1774,7 +1777,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="101" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G8" s="102">
         <v>8</v>
@@ -1797,16 +1800,16 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="125" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="92"/>
       <c r="E10" s="93"/>
       <c r="F10" s="94"/>
       <c r="G10" s="57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H10" s="58"/>
       <c r="I10" s="74"/>
@@ -1816,13 +1819,13 @@
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="125"/>
       <c r="C11" s="55" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" s="99"/>
       <c r="E11" s="100"/>
       <c r="F11" s="101"/>
       <c r="G11" s="55" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H11" s="56"/>
       <c r="I11" s="71"/>
@@ -1831,12 +1834,12 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D14" s="125" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E14" s="125"/>
       <c r="F14" s="125"/>
       <c r="G14" s="125" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H14" s="125"/>
       <c r="I14" s="125"/>
@@ -1852,22 +1855,22 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D15" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>126</v>
-      </c>
       <c r="G15" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="44" t="s">
         <v>124</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>126</v>
       </c>
       <c r="J15" s="125"/>
       <c r="K15" s="125"/>
@@ -1891,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FFE666-9548-4978-AD59-82159C4DB165}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultColWidth="5.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.453125" customWidth="1"/>
@@ -1905,20 +1908,22 @@
     <col min="13" max="13" width="5.26953125" customWidth="1"/>
     <col min="14" max="14" width="55.26953125" customWidth="1"/>
     <col min="15" max="15" width="31" customWidth="1"/>
+    <col min="17" max="17" width="8.453125" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D1" s="52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="132" t="s">
         <v>4</v>
@@ -1936,7 +1941,7 @@
       <c r="L1" s="132"/>
       <c r="M1" s="133"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="44" t="s">
         <v>26</v>
       </c>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>0</v>
@@ -1975,10 +1980,18 @@
         <v>49</v>
       </c>
       <c r="N2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="Q2">
+        <f>J2*M2*2</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>(J2*M2+G2*J2+G2*M2)*2</f>
+        <v>3626</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="44" t="s">
         <v>27</v>
       </c>
@@ -1987,7 +2000,7 @@
       </c>
       <c r="C3" s="42"/>
       <c r="D3" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>0</v>
@@ -2017,10 +2030,18 @@
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q21" si="0">J3*M3*2</f>
+        <v>462</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R21" si="1">(J3*M3+G3*J3+G3*M3)*2</f>
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="44" t="s">
         <v>28</v>
       </c>
@@ -2029,7 +2050,7 @@
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>0</v>
@@ -2059,10 +2080,18 @@
         <v>6</v>
       </c>
       <c r="N4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="44" t="s">
         <v>29</v>
       </c>
@@ -2071,7 +2100,7 @@
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>0</v>
@@ -2101,10 +2130,18 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>117</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>608</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="79" t="s">
         <v>30</v>
       </c>
@@ -2113,7 +2150,7 @@
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="43" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>0</v>
@@ -2143,21 +2180,29 @@
         <v>6</v>
       </c>
       <c r="N6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B7" s="44" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>0</v>
@@ -2186,19 +2231,27 @@
       <c r="M7" s="11">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>4310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="80" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B8" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="80" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" s="81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" s="82" t="s">
         <v>0</v>
@@ -2228,24 +2281,32 @@
         <v>5</v>
       </c>
       <c r="N8" s="85" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="O8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="80" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B9" s="80" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="80" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" s="81" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E9" s="87" t="s">
         <v>0</v>
@@ -2275,24 +2336,32 @@
         <v>31</v>
       </c>
       <c r="N9" s="85" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>0</v>
@@ -2321,19 +2390,27 @@
       <c r="M10" s="20">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="44" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B11" s="44" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>0</v>
@@ -2362,19 +2439,27 @@
       <c r="M11" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>0</v>
@@ -2403,19 +2488,27 @@
       <c r="M12" s="20">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>7336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>0</v>
@@ -2445,21 +2538,29 @@
         <v>53</v>
       </c>
       <c r="O13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>2756</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>8444</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>0</v>
@@ -2489,24 +2590,32 @@
         <v>54</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>4644</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>10270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B15" s="44" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>0</v>
@@ -2536,21 +2645,29 @@
         <v>49</v>
       </c>
       <c r="O15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>2156</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>7410</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B16" s="44" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>0</v>
@@ -2580,21 +2697,29 @@
         <v>40</v>
       </c>
       <c r="O16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>7440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B17" s="39" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E17" s="40" t="s">
         <v>0</v>
@@ -2602,8 +2727,8 @@
       <c r="F17" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="41" t="s">
-        <v>37</v>
+      <c r="G17" s="41">
+        <v>18</v>
       </c>
       <c r="H17" s="46" t="s">
         <v>15</v>
@@ -2623,22 +2748,33 @@
       <c r="M17" s="45">
         <v>39</v>
       </c>
+      <c r="N17" s="136" t="s">
+        <v>150</v>
+      </c>
       <c r="O17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>2184</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B18" s="44" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>0</v>
@@ -2646,8 +2782,8 @@
       <c r="F18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>38</v>
+      <c r="G18" s="14">
+        <v>18</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>8</v>
@@ -2667,22 +2803,33 @@
       <c r="M18" s="3">
         <v>32</v>
       </c>
+      <c r="N18" s="136" t="s">
+        <v>151</v>
+      </c>
       <c r="O18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>2496</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>5052</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>0</v>
@@ -2712,21 +2859,29 @@
         <v>23</v>
       </c>
       <c r="O19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>0</v>
@@ -2756,21 +2911,29 @@
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>0</v>
@@ -2800,10 +2963,18 @@
         <v>36</v>
       </c>
       <c r="O21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="0"/>
+        <v>1440</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>6816</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="44"/>
       <c r="B22" s="44"/>
       <c r="C22" s="44"/>
@@ -2814,7 +2985,7 @@
       <c r="K22" s="6"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="44" t="s">
         <v>33</v>
       </c>
@@ -2836,7 +3007,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="44"/>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -2856,7 +3027,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D25" s="3"/>
       <c r="H25" s="2" t="s">
         <v>8</v>
@@ -2868,7 +3039,7 @@
       <c r="K25" s="6"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D26" s="3"/>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -2880,7 +3051,7 @@
       <c r="K26" s="6"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D27" s="3"/>
       <c r="H27" s="2" t="s">
         <v>8</v>
@@ -2892,33 +3063,33 @@
       <c r="K27" s="6"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D28" s="3"/>
       <c r="H28" s="2"/>
       <c r="J28" s="3"/>
       <c r="K28" s="6"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D29" s="3"/>
       <c r="H29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="6"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D30" s="3"/>
       <c r="H30" s="2"/>
       <c r="J30" s="3"/>
       <c r="K30" s="6"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D31" s="3"/>
       <c r="H31" s="2"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D32" s="3"/>
       <c r="H32" s="2"/>
       <c r="J32" s="3"/>
@@ -2953,16 +3124,16 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="59" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D1" s="69" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="61"/>
       <c r="F1" s="61"/>
@@ -2971,185 +3142,185 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="63"/>
       <c r="B2" s="50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2" s="64"/>
       <c r="H2" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="63"/>
       <c r="B3" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G3" s="64"/>
       <c r="H3" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="63"/>
       <c r="B4" s="50" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4" s="64"/>
       <c r="H4" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="63"/>
       <c r="B5" s="50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" s="64"/>
       <c r="H5" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="63"/>
       <c r="B6" s="50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6" s="64"/>
       <c r="H6" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="63"/>
       <c r="B7" s="50" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="89"/>
       <c r="B8" s="90" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" s="90" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" s="91" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" s="90"/>
       <c r="F8" s="90"/>
       <c r="G8" s="91"/>
       <c r="H8" s="90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I8" s="90" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="63"/>
       <c r="B9" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="63"/>
       <c r="B10" s="50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G10" s="64"/>
       <c r="H10" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="122" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B11" s="123" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C11" s="123" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" s="124" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" s="123"/>
       <c r="F11" s="123"/>
       <c r="G11" s="124"/>
       <c r="H11" s="90"/>
       <c r="I11" s="90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="67" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E12" s="66"/>
       <c r="F12" s="66"/>
@@ -3178,16 +3349,16 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="59" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="135" t="s">
         <v>4</v>
@@ -3205,39 +3376,39 @@
       <c r="L1" s="135"/>
       <c r="M1" s="135"/>
       <c r="N1" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O1" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="63" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" s="110" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="110" t="s">
         <v>139</v>
-      </c>
-      <c r="F2" s="110" t="s">
-        <v>141</v>
       </c>
       <c r="G2" s="111">
         <v>8</v>
       </c>
       <c r="H2" s="112" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I2" s="113" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J2" s="114">
         <v>3</v>
@@ -3260,31 +3431,31 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="63" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="110" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F3" s="110" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G3" s="111">
         <v>12</v>
       </c>
       <c r="H3" s="112" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I3" s="113" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J3" s="114">
         <v>10</v>
@@ -3293,7 +3464,7 @@
         <v>6</v>
       </c>
       <c r="L3" s="110" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M3" s="114">
         <v>23</v>
@@ -3307,19 +3478,19 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E4" s="110" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F4" s="110" t="s">
         <v>32</v>
@@ -3337,10 +3508,10 @@
         <v>9</v>
       </c>
       <c r="K4" s="115" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L4" s="110" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M4" s="114">
         <v>25</v>
@@ -3354,22 +3525,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="63" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" s="110" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="110" t="s">
         <v>139</v>
-      </c>
-      <c r="F5" s="110" t="s">
-        <v>141</v>
       </c>
       <c r="G5" s="111">
         <v>9</v>
@@ -3378,16 +3549,16 @@
         <v>6</v>
       </c>
       <c r="I5" s="113" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J5" s="114">
         <v>11</v>
       </c>
       <c r="K5" s="115" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L5" s="110" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M5" s="114">
         <v>38</v>
@@ -3401,19 +3572,19 @@
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="116" t="s">
         <v>137</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="64" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="116" t="s">
-        <v>139</v>
       </c>
       <c r="F6" s="116" t="s">
         <v>32</v>
@@ -3422,10 +3593,10 @@
         <v>18</v>
       </c>
       <c r="H6" s="118" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I6" s="119" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J6" s="120">
         <v>17</v>
@@ -3434,7 +3605,7 @@
         <v>6</v>
       </c>
       <c r="L6" s="116" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M6" s="120">
         <v>19</v>
@@ -3449,21 +3620,21 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="63"/>
       <c r="D7" s="64" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G7" s="64"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="63"/>
       <c r="D8" s="64" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G8" s="64"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="63"/>
       <c r="D9" s="64" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G9" s="64"/>
     </row>
@@ -3481,7 +3652,7 @@
       <c r="F11" s="61"/>
       <c r="G11" s="62"/>
       <c r="N11" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/sessions_summary.xlsx
+++ b/sessions_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Storage\MATLAB\ThalamocorticalLoop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D001818-A0D5-41DE-8CAB-1F04FFECAF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC87153-0C90-4F16-A4BF-A432F923C44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="3" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="6" r:id="rId1"/>
@@ -20,10 +20,21 @@
     <sheet name="Lemmy-Kaining" sheetId="3" r:id="rId5"/>
     <sheet name="Slayer-Kaining" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1348,9 +1359,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1374,9 +1383,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1414,7 +1423,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1520,7 +1529,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1662,7 +1671,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2748,7 +2757,7 @@
       <c r="M17" s="45">
         <v>39</v>
       </c>
-      <c r="N17" s="136" t="s">
+      <c r="N17" s="1" t="s">
         <v>150</v>
       </c>
       <c r="O17" t="s">
@@ -2803,7 +2812,7 @@
       <c r="M18" s="3">
         <v>32</v>
       </c>
-      <c r="N18" s="136" t="s">
+      <c r="N18" s="1" t="s">
         <v>151</v>
       </c>
       <c r="O18" t="s">
@@ -3334,7 +3343,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD31B0A-8ACD-468E-8C67-02F9624BD3CF}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" style="50" customWidth="1"/>
@@ -3347,7 +3356,7 @@
     <col min="16" max="16384" width="29.81640625" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="59" t="s">
         <v>112</v>
       </c>
@@ -3382,7 +3391,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="63" t="s">
         <v>106</v>
       </c>
@@ -3429,7 +3438,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="63" t="s">
         <v>107</v>
       </c>
@@ -3476,7 +3485,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="63" t="s">
         <v>108</v>
       </c>
@@ -3523,7 +3532,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="63" t="s">
         <v>133</v>
       </c>
@@ -3569,8 +3578,16 @@
       <c r="O5">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P5" s="136">
+        <f>2*J5*M5</f>
+        <v>836</v>
+      </c>
+      <c r="Q5" s="136">
+        <f>2*(G5*J5+G5*M5+J5*M5)</f>
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="63" t="s">
         <v>135</v>
       </c>
@@ -3616,34 +3633,42 @@
       <c r="O6">
         <v>187</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P6" s="136">
+        <f>2*J6*M6</f>
+        <v>646</v>
+      </c>
+      <c r="Q6" s="136">
+        <f>2*(G6*J6+G6*M6+J6*M6)</f>
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="63"/>
       <c r="D7" s="64" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="64"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="63"/>
       <c r="D8" s="64" t="s">
         <v>91</v>
       </c>
       <c r="G8" s="64"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="63"/>
       <c r="D9" s="64" t="s">
         <v>92</v>
       </c>
       <c r="G9" s="64"/>
     </row>
-    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="63"/>
       <c r="D10" s="64"/>
       <c r="G10" s="64"/>
     </row>
-    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="68"/>
       <c r="B11" s="61"/>
       <c r="C11" s="61"/>
@@ -3655,7 +3680,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="65"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>

--- a/sessions_summary.xlsx
+++ b/sessions_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Storage\MATLAB\ThalamocorticalLoop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pri\Storage\Projects\ThalamoCorticalNetwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC87153-0C90-4F16-A4BF-A432F923C44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52230738-E0DB-4356-A344-E636166FEE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="3" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
+    <workbookView xWindow="-18120" yWindow="-11115" windowWidth="18240" windowHeight="28320" activeTab="1" xr2:uid="{56367E76-6CBF-4746-8F91-48887379FCA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="160">
   <si>
     <t>P3</t>
   </si>
@@ -497,6 +497,30 @@
   </si>
   <si>
     <t>Thal 35-18</t>
+  </si>
+  <si>
+    <t>ctx across</t>
+  </si>
+  <si>
+    <t>all across</t>
+  </si>
+  <si>
+    <t>Muscimol total</t>
+  </si>
+  <si>
+    <t>Saline total</t>
+  </si>
+  <si>
+    <t>across</t>
+  </si>
+  <si>
+    <t>within</t>
+  </si>
+  <si>
+    <t>ctx within</t>
+  </si>
+  <si>
+    <t>all within</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1326,6 +1350,9 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1356,10 +1383,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1680,34 +1703,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E51CD7-F882-46FB-A302-DE4F0A9E1B83}">
   <dimension ref="B3:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="4" max="6" width="12.81640625" style="105" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="6" width="12.85546875" style="105" customWidth="1"/>
     <col min="7" max="11" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="129" t="s">
+    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="D4" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="131" t="s">
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="128"/>
-    </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="130"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="129"/>
+    </row>
+    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="131"/>
       <c r="D5" s="106" t="s">
         <v>127</v>
       </c>
@@ -1733,7 +1756,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C6" s="57" t="s">
         <v>82</v>
       </c>
@@ -1754,7 +1777,7 @@
       <c r="J6" s="75"/>
       <c r="K6" s="57"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C7" s="54" t="s">
         <v>83</v>
       </c>
@@ -1775,7 +1798,7 @@
       <c r="J7" s="76"/>
       <c r="K7" s="54"/>
     </row>
-    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C8" s="55" t="s">
         <v>84</v>
       </c>
@@ -1796,7 +1819,7 @@
       <c r="J8" s="77"/>
       <c r="K8" s="55"/>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="72"/>
       <c r="D9" s="106"/>
       <c r="E9" s="107"/>
@@ -1807,8 +1830,8 @@
       <c r="J9" s="2"/>
       <c r="K9" s="72"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="125" t="s">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="126" t="s">
         <v>86</v>
       </c>
       <c r="C10" s="57" t="s">
@@ -1825,8 +1848,8 @@
       <c r="J10" s="75"/>
       <c r="K10" s="57"/>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="125"/>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="126"/>
       <c r="C11" s="55" t="s">
         <v>82</v>
       </c>
@@ -1841,28 +1864,28 @@
       <c r="J11" s="77"/>
       <c r="K11" s="55"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D14" s="125" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D14" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125" t="s">
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125" t="s">
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="125" t="s">
+      <c r="K14" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="125" t="s">
+      <c r="L14" s="126" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D15" s="44" t="s">
         <v>122</v>
       </c>
@@ -1881,9 +1904,9 @@
       <c r="I15" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1903,25 +1926,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FFE666-9548-4978-AD59-82159C4DB165}">
-  <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultColWidth="5.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:U33"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="5.453125" style="1"/>
-    <col min="7" max="7" width="6.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.453125" style="1"/>
-    <col min="12" max="12" width="4.1796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.26953125" customWidth="1"/>
-    <col min="14" max="14" width="55.26953125" customWidth="1"/>
-    <col min="15" max="15" width="31" customWidth="1"/>
-    <col min="17" max="17" width="8.453125" customWidth="1"/>
-    <col min="18" max="18" width="12.54296875" customWidth="1"/>
+    <col min="5" max="6" width="5.42578125" style="1"/>
+    <col min="7" max="7" width="6.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.42578125" style="1"/>
+    <col min="12" max="12" width="4.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="8.85546875" customWidth="1"/>
+    <col min="18" max="21" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
         <v>112</v>
       </c>
@@ -1934,23 +1958,35 @@
       <c r="D1" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="132" t="s">
+      <c r="E1" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="132"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="134" t="s">
+      <c r="F1" s="133"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="132"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="134" t="s">
+      <c r="I1" s="133"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="132"/>
-      <c r="M1" s="133"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="L1" s="133"/>
+      <c r="M1" s="134"/>
+      <c r="R1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S1" t="s">
+        <v>153</v>
+      </c>
+      <c r="T1" t="s">
+        <v>158</v>
+      </c>
+      <c r="U1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
         <v>26</v>
       </c>
@@ -1991,16 +2027,24 @@
       <c r="N2" t="s">
         <v>117</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <f>J2*M2*2</f>
         <v>0</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <f>(J2*M2+G2*J2+G2*M2)*2</f>
         <v>3626</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T2">
+        <f>J2*(J2-1)+M2*(M2-1)</f>
+        <v>2352</v>
+      </c>
+      <c r="U2">
+        <f>J2*(J2-1)+M2*(M2-1)+G2*(G2-1)</f>
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="s">
         <v>27</v>
       </c>
@@ -2041,16 +2085,24 @@
       <c r="N3" t="s">
         <v>117</v>
       </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="0">J3*M3*2</f>
+      <c r="R3">
+        <f t="shared" ref="R3:R21" si="0">J3*M3*2</f>
         <v>462</v>
       </c>
-      <c r="R3">
-        <f t="shared" ref="R3:R21" si="1">(J3*M3+G3*J3+G3*M3)*2</f>
+      <c r="S3">
+        <f t="shared" ref="S3:S21" si="1">(J3*M3+G3*J3+G3*M3)*2</f>
         <v>3022</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T3">
+        <f t="shared" ref="T3:T21" si="2">J3*(J3-1)+M3*(M3-1)</f>
+        <v>530</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U21" si="3">J3*(J3-1)+M3*(M3-1)+G3*(G3-1)</f>
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="s">
         <v>28</v>
       </c>
@@ -2091,16 +2143,24 @@
       <c r="N4" t="s">
         <v>117</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <f t="shared" si="0"/>
         <v>540</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <f t="shared" si="1"/>
         <v>948</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T4">
+        <f t="shared" si="2"/>
+        <v>2010</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="3"/>
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>29</v>
       </c>
@@ -2141,16 +2201,24 @@
       <c r="N5" t="s">
         <v>117</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <f t="shared" si="0"/>
         <v>608</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <f t="shared" si="1"/>
         <v>4318</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T5">
+        <f t="shared" si="2"/>
+        <v>582</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="3"/>
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79" t="s">
         <v>30</v>
       </c>
@@ -2191,16 +2259,24 @@
       <c r="N6" t="s">
         <v>117</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <f t="shared" si="1"/>
         <v>306</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T6">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
         <v>60</v>
       </c>
@@ -2240,16 +2316,24 @@
       <c r="M7" s="11">
         <v>19</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <f t="shared" si="0"/>
         <v>570</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <f t="shared" si="1"/>
         <v>4310</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T7">
+        <f t="shared" si="2"/>
+        <v>552</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="3"/>
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="80" t="s">
         <v>114</v>
       </c>
@@ -2295,16 +2379,24 @@
       <c r="O8" t="s">
         <v>125</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <f t="shared" si="1"/>
         <v>1966</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T8">
+        <f t="shared" si="2"/>
+        <v>260</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="3"/>
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="80" t="s">
         <v>62</v>
       </c>
@@ -2350,16 +2442,24 @@
       <c r="O9" t="s">
         <v>125</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <f t="shared" si="1"/>
         <v>3968</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T9">
+        <f t="shared" si="2"/>
+        <v>930</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="3"/>
+        <v>4962</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>63</v>
       </c>
@@ -2399,16 +2499,24 @@
       <c r="M10" s="20">
         <v>26</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T10">
+        <f t="shared" si="2"/>
+        <v>650</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="3"/>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
         <v>64</v>
       </c>
@@ -2448,16 +2556,24 @@
       <c r="M11" s="25">
         <v>0</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <f t="shared" si="1"/>
         <v>1620</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T11">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="3"/>
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
         <v>65</v>
       </c>
@@ -2497,16 +2613,24 @@
       <c r="M12" s="20">
         <v>25</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <f t="shared" si="1"/>
         <v>7336</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T12">
+        <f t="shared" si="2"/>
+        <v>1356</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="3"/>
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
         <v>66</v>
       </c>
@@ -2549,16 +2673,24 @@
       <c r="O13" t="s">
         <v>116</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <f t="shared" si="0"/>
         <v>2756</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <f t="shared" si="1"/>
         <v>8444</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T13">
+        <f t="shared" si="2"/>
+        <v>3406</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="3"/>
+        <v>4666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
         <v>67</v>
       </c>
@@ -2604,16 +2736,24 @@
       <c r="O14" t="s">
         <v>116</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <f t="shared" si="0"/>
         <v>4644</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <f t="shared" si="1"/>
         <v>10270</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T14">
+        <f t="shared" si="2"/>
+        <v>4668</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="3"/>
+        <v>5480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
         <v>68</v>
       </c>
@@ -2656,16 +2796,24 @@
       <c r="O15" t="s">
         <v>116</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <f t="shared" si="0"/>
         <v>2156</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <f t="shared" si="1"/>
         <v>7410</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T15">
+        <f t="shared" si="2"/>
+        <v>2814</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="3"/>
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
         <v>69</v>
       </c>
@@ -2708,16 +2856,24 @@
       <c r="O16" t="s">
         <v>116</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <f t="shared" si="1"/>
         <v>7440</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T16">
+        <f t="shared" si="2"/>
+        <v>2430</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="3"/>
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>70</v>
       </c>
@@ -2763,16 +2919,24 @@
       <c r="O17" t="s">
         <v>116</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <f t="shared" si="0"/>
         <v>2184</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <f t="shared" si="1"/>
         <v>4596</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T17">
+        <f t="shared" si="2"/>
+        <v>2238</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="3"/>
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
         <v>71</v>
       </c>
@@ -2818,16 +2982,24 @@
       <c r="O18" t="s">
         <v>116</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <f t="shared" si="0"/>
         <v>2496</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f t="shared" si="1"/>
         <v>5052</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T18">
+        <f t="shared" si="2"/>
+        <v>2474</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="3"/>
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
         <v>72</v>
       </c>
@@ -2870,16 +3042,24 @@
       <c r="O19" t="s">
         <v>116</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <f t="shared" si="1"/>
         <v>2554</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T19">
+        <f t="shared" si="2"/>
+        <v>886</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="3"/>
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
         <v>73</v>
       </c>
@@ -2922,16 +3102,24 @@
       <c r="O20" t="s">
         <v>116</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <f t="shared" si="0"/>
         <v>520</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f t="shared" si="1"/>
         <v>2752</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T20">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="3"/>
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
         <v>74</v>
       </c>
@@ -2974,16 +3162,24 @@
       <c r="O21" t="s">
         <v>116</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <f t="shared" si="1"/>
         <v>6816</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T21">
+        <f t="shared" si="2"/>
+        <v>1640</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="3"/>
+        <v>3896</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="44"/>
       <c r="C22" s="44"/>
@@ -2994,7 +3190,7 @@
       <c r="K22" s="6"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
         <v>33</v>
       </c>
@@ -3016,7 +3212,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -3036,7 +3232,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D25" s="3"/>
       <c r="H25" s="2" t="s">
         <v>8</v>
@@ -3048,7 +3244,7 @@
       <c r="K25" s="6"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D26" s="3"/>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3059,8 +3255,20 @@
       <c r="J26" s="3"/>
       <c r="K26" s="6"/>
       <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R26" t="s">
+        <v>152</v>
+      </c>
+      <c r="S26" t="s">
+        <v>156</v>
+      </c>
+      <c r="T26" t="s">
+        <v>158</v>
+      </c>
+      <c r="U26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D27" s="3"/>
       <c r="H27" s="2" t="s">
         <v>8</v>
@@ -3071,39 +3279,77 @@
       <c r="J27" s="3"/>
       <c r="K27" s="6"/>
       <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="Q27" t="s">
+        <v>154</v>
+      </c>
+      <c r="R27">
+        <f>R7+SUM(R10:R16)</f>
+        <v>13926</v>
+      </c>
+      <c r="S27">
+        <f>S7+SUM(S10:S16)</f>
+        <v>47090</v>
+      </c>
+      <c r="T27">
+        <f>T7+SUM(T10:T16)</f>
+        <v>16086</v>
+      </c>
+      <c r="U27">
+        <f>U7+SUM(U10:U16)</f>
+        <v>29682</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D28" s="3"/>
       <c r="H28" s="2"/>
       <c r="J28" s="3"/>
       <c r="K28" s="6"/>
       <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="Q28" t="s">
+        <v>155</v>
+      </c>
+      <c r="R28">
+        <f>SUM(R17:R21)</f>
+        <v>7560</v>
+      </c>
+      <c r="S28">
+        <f>SUM(S17:S21)</f>
+        <v>21770</v>
+      </c>
+      <c r="T28">
+        <f>SUM(T17:T21)</f>
+        <v>7978</v>
+      </c>
+      <c r="U28">
+        <f>SUM(U17:U21)</f>
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>
       <c r="H29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="6"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D30" s="3"/>
       <c r="H30" s="2"/>
       <c r="J30" s="3"/>
       <c r="K30" s="6"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D31" s="3"/>
       <c r="H31" s="2"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D32" s="3"/>
       <c r="H32" s="2"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D33" s="3"/>
       <c r="H33" s="2"/>
       <c r="J33" s="3"/>
@@ -3123,15 +3369,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC68E12D-C9CD-4DEC-A7DD-D60B42882618}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="29.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" style="50" customWidth="1"/>
-    <col min="2" max="4" width="17.26953125" style="50" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" style="50" customWidth="1"/>
-    <col min="6" max="16384" width="29.81640625" style="50"/>
+    <col min="1" max="1" width="19.85546875" style="50" customWidth="1"/>
+    <col min="2" max="4" width="17.28515625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" style="50" customWidth="1"/>
+    <col min="6" max="16384" width="29.85546875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="59" t="s">
         <v>112</v>
       </c>
@@ -3148,7 +3394,7 @@
       <c r="F1" s="61"/>
       <c r="G1" s="62"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="63"/>
       <c r="B2" s="50" t="s">
         <v>40</v>
@@ -3164,7 +3410,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="63"/>
       <c r="B3" s="50" t="s">
         <v>41</v>
@@ -3180,7 +3426,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="63"/>
       <c r="B4" s="50" t="s">
         <v>42</v>
@@ -3196,7 +3442,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="63"/>
       <c r="B5" s="50" t="s">
         <v>43</v>
@@ -3212,7 +3458,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="63"/>
       <c r="B6" s="50" t="s">
         <v>44</v>
@@ -3228,7 +3474,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="63"/>
       <c r="B7" s="50" t="s">
         <v>45</v>
@@ -3244,7 +3490,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="89"/>
       <c r="B8" s="90" t="s">
         <v>46</v>
@@ -3265,7 +3511,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
       <c r="B9" s="50" t="s">
         <v>47</v>
@@ -3281,7 +3527,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="63"/>
       <c r="B10" s="50" t="s">
         <v>48</v>
@@ -3297,7 +3543,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="122" t="s">
         <v>75</v>
       </c>
@@ -3318,7 +3564,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>76</v>
       </c>
@@ -3344,19 +3590,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD31B0A-8ACD-468E-8C67-02F9624BD3CF}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="29.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" style="50" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" style="50" customWidth="1"/>
-    <col min="4" max="4" width="23.1796875" style="50" customWidth="1"/>
-    <col min="5" max="13" width="6.453125" style="50" customWidth="1"/>
-    <col min="14" max="14" width="24.54296875" style="50" customWidth="1"/>
-    <col min="15" max="15" width="16.453125" style="50" customWidth="1"/>
-    <col min="16" max="16384" width="29.81640625" style="50"/>
+    <col min="1" max="1" width="18.85546875" style="50" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="50" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="50" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="50" customWidth="1"/>
+    <col min="5" max="13" width="6.42578125" style="50" customWidth="1"/>
+    <col min="14" max="14" width="24.5703125" style="50" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="50" customWidth="1"/>
+    <col min="16" max="16384" width="29.85546875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="59" t="s">
         <v>112</v>
       </c>
@@ -3369,21 +3615,21 @@
       <c r="D1" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="135" t="s">
+      <c r="E1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135" t="s">
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
       <c r="N1" s="50" t="s">
         <v>144</v>
       </c>
@@ -3391,7 +3637,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
         <v>106</v>
       </c>
@@ -3438,7 +3684,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
         <v>107</v>
       </c>
@@ -3485,7 +3731,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
         <v>108</v>
       </c>
@@ -3532,7 +3778,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
         <v>133</v>
       </c>
@@ -3578,16 +3824,16 @@
       <c r="O5">
         <v>90</v>
       </c>
-      <c r="P5" s="136">
+      <c r="P5">
         <f>2*J5*M5</f>
         <v>836</v>
       </c>
-      <c r="Q5" s="136">
+      <c r="Q5">
         <f>2*(G5*J5+G5*M5+J5*M5)</f>
         <v>1718</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="63" t="s">
         <v>135</v>
       </c>
@@ -3633,42 +3879,42 @@
       <c r="O6">
         <v>187</v>
       </c>
-      <c r="P6" s="136">
+      <c r="P6">
         <f>2*J6*M6</f>
         <v>646</v>
       </c>
-      <c r="Q6" s="136">
+      <c r="Q6">
         <f>2*(G6*J6+G6*M6+J6*M6)</f>
         <v>1942</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="63"/>
       <c r="D7" s="64" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="64"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="63"/>
       <c r="D8" s="64" t="s">
         <v>91</v>
       </c>
       <c r="G8" s="64"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
       <c r="D9" s="64" t="s">
         <v>92</v>
       </c>
       <c r="G9" s="64"/>
     </row>
-    <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="63"/>
       <c r="D10" s="64"/>
       <c r="G10" s="64"/>
     </row>
-    <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="68"/>
       <c r="B11" s="61"/>
       <c r="C11" s="61"/>
@@ -3680,7 +3926,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
@@ -3703,7 +3949,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624E48F4-7931-4929-AE47-4DEF71FFC465}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3712,7 +3958,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD8B24D-05CA-4D65-9A42-9A76302C7CF2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
